--- a/output/pdf_financials_xlsx/DELX.xlsx
+++ b/output/pdf_financials_xlsx/DELX.xlsx
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.16253</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.0462</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.177523</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0.332026</v>
@@ -12310,7 +12310,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -13400,7 +13404,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DELX.xlsx
+++ b/output/pdf_financials_xlsx/DELX.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.177479</v>
+        <v>2.100065</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>8.498953999999999</v>
@@ -803,10 +803,10 @@
         <v>4.496063</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.050109</v>
+        <v>4.262312</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.011338</v>
+        <v>4.778506</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -1825,28 +1825,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.089992</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.187634</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.135639</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.47263</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.263569</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.136172</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.054262</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.047575</v>
       </c>
     </row>
     <row r="35">
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.089992</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.187634</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.135639</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.47263</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.263569</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.136172</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.054262</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.047575</v>
       </c>
     </row>
     <row r="37">
@@ -2329,28 +2329,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.218315</v>
+        <v>4.128323</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.431478</v>
+        <v>0.243844</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.269414</v>
+        <v>0.133775</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.664685</v>
+        <v>0.192055</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.475193</v>
+        <v>0.211624</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.237078</v>
+        <v>0.100906</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.160888</v>
+        <v>0.106626</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.117514</v>
+        <v>0.069939</v>
       </c>
     </row>
     <row r="49">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22041,7 +22041,7 @@
         <v>8.505131</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>-4.858204</v>
+        <v>4.858204</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">

--- a/output/pdf_financials_xlsx/DELX.xlsx
+++ b/output/pdf_financials_xlsx/DELX.xlsx
@@ -1587,10 +1587,10 @@
         <v>0.010417</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.035936</v>
+        <v>0.009535999999999999</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.00731</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.10638</v>
@@ -1629,7 +1629,7 @@
         <v>-1.883935</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.677925</v>
+        <v>-8.704325000000001</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>1.000132</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.672994</v>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
@@ -4991,19 +4991,19 @@
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>2.585279</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>2.069249</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>1.689404</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>2.235466</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>1.79418</v>
       </c>
     </row>
     <row r="121">
@@ -14488,7 +14488,11 @@
           <t>Issuance of common shares (net of issuance costs)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -17795,7 +17799,11 @@
           <t>Issuance of common shares (net of issuance costs) 615,215</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -21044,7 +21052,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">

--- a/output/pdf_financials_xlsx/DELX.xlsx
+++ b/output/pdf_financials_xlsx/DELX.xlsx
@@ -4631,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>-0.201772</v>
+        <v>-0.004903</v>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.018489</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>-0.201772</v>
+        <v>-0.004903</v>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>-4.441144</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.009169</v>
+        <v>-1.8123</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
@@ -11074,7 +11074,11 @@
           <t>Lease liabilities (note 12)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -12003,7 +12007,11 @@
           <t>Lease liabilities (note 14)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -17246,7 +17254,11 @@
           <t>Purchase of equipment -</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -19169,7 +19181,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
